--- a/src/DashboardApp/pop_final.xlsx
+++ b/src/DashboardApp/pop_final.xlsx
@@ -37,151 +37,151 @@
     <t>[1, 1, 2, 4, 16]</t>
   </si>
   <si>
-    <t>[21, 1, 6, 9, 19]</t>
-  </si>
-  <si>
-    <t>[25, 1, 4, 16, 8]</t>
-  </si>
-  <si>
-    <t>[2, 4, 18, 27, 31]</t>
-  </si>
-  <si>
-    <t>[1, 13, 26, 14, 28]</t>
-  </si>
-  <si>
-    <t>[7, 28, 14, 23, 29]</t>
-  </si>
-  <si>
-    <t>[6, 0, 7, 4, 8]</t>
-  </si>
-  <si>
-    <t>[15, 12, 0, 27, 16]</t>
-  </si>
-  <si>
-    <t>[19, 25, 8, 19, 15]</t>
-  </si>
-  <si>
-    <t>[12, 30, 4, 16, 13]</t>
-  </si>
-  <si>
-    <t>[9, 19, 26, 15, 19]</t>
-  </si>
-  <si>
-    <t>[20, 30, 18, 13, 23]</t>
-  </si>
-  <si>
-    <t>[23, 5, 13, 11, 22]</t>
-  </si>
-  <si>
-    <t>[22, 29, 9, 16, 13]</t>
-  </si>
-  <si>
-    <t>[2, 7, 18, 12, 7]</t>
-  </si>
-  <si>
-    <t>[27, 1, 20, 25, 9]</t>
-  </si>
-  <si>
-    <t>[19, 2, 19, 19, 23]</t>
-  </si>
-  <si>
-    <t>[21, 7, 18, 25, 3]</t>
-  </si>
-  <si>
-    <t>[16, 14, 17, 29, 13]</t>
-  </si>
-  <si>
-    <t>[22, 31, 31, 14, 29]</t>
-  </si>
-  <si>
-    <t>[24, 19, 4, 31, 5]</t>
-  </si>
-  <si>
-    <t>[27, 11, 6, 12, 23]</t>
-  </si>
-  <si>
-    <t>[25, 8, 24, 29, 17]</t>
-  </si>
-  <si>
-    <t>[6, 27, 16, 30, 30]</t>
-  </si>
-  <si>
-    <t>[12, 22, 13, 11, 17]</t>
-  </si>
-  <si>
-    <t>[27, 2, 22, 21, 10]</t>
-  </si>
-  <si>
-    <t>[17, 2, 17, 11, 2]</t>
-  </si>
-  <si>
-    <t>[18, 28, 5, 10, 3]</t>
-  </si>
-  <si>
-    <t>[30, 10, 10, 3, 20]</t>
-  </si>
-  <si>
-    <t>[11, 31, 28, 15, 2]</t>
-  </si>
-  <si>
-    <t>[7, 2, 26, 28, 5]</t>
-  </si>
-  <si>
-    <t>[30, 16, 19, 7, 24]</t>
-  </si>
-  <si>
-    <t>[23, 4, 4, 7, 31]</t>
-  </si>
-  <si>
-    <t>[19, 22, 22, 21, 10]</t>
-  </si>
-  <si>
-    <t>[31, 25, 7, 22, 19]</t>
-  </si>
-  <si>
-    <t>[18, 26, 30, 23, 19]</t>
-  </si>
-  <si>
-    <t>[6, 3, 12, 20, 16]</t>
-  </si>
-  <si>
-    <t>[21, 28, 7, 30, 9]</t>
-  </si>
-  <si>
-    <t>[6, 28, 5, 7, 14]</t>
-  </si>
-  <si>
-    <t>[15, 3, 23, 0, 2]</t>
-  </si>
-  <si>
-    <t>[19, 15, 23, 21, 11]</t>
-  </si>
-  <si>
-    <t>[2, 28, 4, 21, 25]</t>
-  </si>
-  <si>
-    <t>[15, 3, 20, 28, 17]</t>
-  </si>
-  <si>
-    <t>[28, 14, 7, 23, 6]</t>
-  </si>
-  <si>
-    <t>[24, 28, 4, 25, 22]</t>
-  </si>
-  <si>
-    <t>[14, 16, 23, 12, 8]</t>
-  </si>
-  <si>
-    <t>[23, 27, 11, 29, 14]</t>
-  </si>
-  <si>
-    <t>[15, 27, 20, 14, 3]</t>
-  </si>
-  <si>
-    <t>[18, 2, 7, 3, 30]</t>
-  </si>
-  <si>
-    <t>[25, 10, 23, 19, 9]</t>
+    <t>[14, 23, 29, 25, 29]</t>
+  </si>
+  <si>
+    <t>[30, 4, 10, 6, 26]</t>
+  </si>
+  <si>
+    <t>[5, 3, 1, 6, 29]</t>
+  </si>
+  <si>
+    <t>[15, 7, 21, 31, 19]</t>
+  </si>
+  <si>
+    <t>[13, 7, 8, 17, 7]</t>
+  </si>
+  <si>
+    <t>[22, 10, 0, 22, 25]</t>
+  </si>
+  <si>
+    <t>[4, 24, 10, 11, 16]</t>
+  </si>
+  <si>
+    <t>[24, 18, 25, 4, 23]</t>
+  </si>
+  <si>
+    <t>[8, 21, 0, 25, 1]</t>
+  </si>
+  <si>
+    <t>[24, 17, 11, 0, 23]</t>
+  </si>
+  <si>
+    <t>[22, 24, 14, 27, 23]</t>
+  </si>
+  <si>
+    <t>[14, 2, 29, 25, 1]</t>
+  </si>
+  <si>
+    <t>[12, 10, 14, 7, 9]</t>
+  </si>
+  <si>
+    <t>[1, 2, 16, 21, 23]</t>
+  </si>
+  <si>
+    <t>[19, 2, 18, 29, 27]</t>
+  </si>
+  <si>
+    <t>[2, 2, 7, 12, 17]</t>
+  </si>
+  <si>
+    <t>[13, 24, 5, 3, 4]</t>
+  </si>
+  <si>
+    <t>[14, 1, 28, 0, 9]</t>
+  </si>
+  <si>
+    <t>[10, 10, 18, 12, 4]</t>
+  </si>
+  <si>
+    <t>[17, 1, 19, 30, 4]</t>
+  </si>
+  <si>
+    <t>[3, 14, 25, 23, 1]</t>
+  </si>
+  <si>
+    <t>[12, 13, 19, 17, 22]</t>
+  </si>
+  <si>
+    <t>[24, 13, 26, 16, 22]</t>
+  </si>
+  <si>
+    <t>[12, 25, 10, 4, 15]</t>
+  </si>
+  <si>
+    <t>[28, 28, 16, 4, 3]</t>
+  </si>
+  <si>
+    <t>[7, 17, 7, 3, 11]</t>
+  </si>
+  <si>
+    <t>[1, 18, 29, 7, 21]</t>
+  </si>
+  <si>
+    <t>[18, 17, 5, 6, 19]</t>
+  </si>
+  <si>
+    <t>[4, 26, 14, 2, 3]</t>
+  </si>
+  <si>
+    <t>[21, 0, 22, 17, 31]</t>
+  </si>
+  <si>
+    <t>[20, 23, 4, 20, 24]</t>
+  </si>
+  <si>
+    <t>[3, 2, 28, 21, 29]</t>
+  </si>
+  <si>
+    <t>[13, 30, 10, 2, 21]</t>
+  </si>
+  <si>
+    <t>[11, 27, 25, 18, 7]</t>
+  </si>
+  <si>
+    <t>[9, 2, 20, 15, 12]</t>
+  </si>
+  <si>
+    <t>[23, 7, 21, 29, 25]</t>
+  </si>
+  <si>
+    <t>[15, 23, 24, 19, 5]</t>
+  </si>
+  <si>
+    <t>[11, 0, 23, 17, 15]</t>
+  </si>
+  <si>
+    <t>[26, 26, 5, 2, 17]</t>
+  </si>
+  <si>
+    <t>[14, 13, 2, 5, 19]</t>
+  </si>
+  <si>
+    <t>[28, 27, 19, 22, 9]</t>
+  </si>
+  <si>
+    <t>[13, 14, 14, 0, 19]</t>
+  </si>
+  <si>
+    <t>[6, 26, 29, 28, 30]</t>
+  </si>
+  <si>
+    <t>[17, 1, 20, 23, 14]</t>
+  </si>
+  <si>
+    <t>[4, 18, 9, 10, 10]</t>
+  </si>
+  <si>
+    <t>[5, 13, 21, 12, 4]</t>
+  </si>
+  <si>
+    <t>[12, 28, 6, 20, 14]</t>
+  </si>
+  <si>
+    <t>[6, 20, 6, 14, 9]</t>
+  </si>
+  <si>
+    <t>[17, 11, 23, 29, 17]</t>
   </si>
   <si>
     <t>HOF</t>
@@ -602,10 +602,10 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>19820289</v>
+        <v>130102113</v>
       </c>
       <c r="G3">
-        <v>56</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -622,10 +622,10 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>45089710</v>
+        <v>81179756</v>
       </c>
       <c r="G4">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -642,10 +642,10 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>57542675</v>
+        <v>62245</v>
       </c>
       <c r="G5">
-        <v>82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -662,10 +662,10 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>48707038</v>
+        <v>110378732</v>
       </c>
       <c r="G6">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -682,10 +682,10 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>87328418</v>
+        <v>10966285</v>
       </c>
       <c r="G7">
-        <v>101</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -702,10 +702,10 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>343471</v>
+        <v>44585064</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -722,10 +722,10 @@
         <v>13</v>
       </c>
       <c r="E9">
-        <v>57521294</v>
+        <v>33937319</v>
       </c>
       <c r="G9">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -742,10 +742,10 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>61533873</v>
+        <v>78646903</v>
       </c>
       <c r="G10">
-        <v>86</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -762,10 +762,10 @@
         <v>15</v>
       </c>
       <c r="E11">
-        <v>87487296</v>
+        <v>58634126</v>
       </c>
       <c r="G11">
-        <v>75</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -782,10 +782,10 @@
         <v>16</v>
       </c>
       <c r="E12">
-        <v>59543809</v>
+        <v>40494386</v>
       </c>
       <c r="G12">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -802,10 +802,10 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>103287735</v>
+        <v>105445915</v>
       </c>
       <c r="G13">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -822,10 +822,10 @@
         <v>18</v>
       </c>
       <c r="E14">
-        <v>30949244</v>
+        <v>109350830</v>
       </c>
       <c r="G14">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -842,10 +842,10 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>96253814</v>
+        <v>6267707</v>
       </c>
       <c r="G15">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -862,10 +862,10 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>11708747</v>
+        <v>23010026</v>
       </c>
       <c r="G16">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -882,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>105044213</v>
+        <v>87871198</v>
       </c>
       <c r="G17">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -902,10 +902,10 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>36032373</v>
+        <v>1751259</v>
       </c>
       <c r="G18">
-        <v>82</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -922,10 +922,10 @@
         <v>23</v>
       </c>
       <c r="E19">
-        <v>66561501</v>
+        <v>34758193</v>
       </c>
       <c r="G19">
-        <v>74</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -942,10 +942,10 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>84380334</v>
+        <v>65349999</v>
       </c>
       <c r="G20">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -962,10 +962,10 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>199483110</v>
+        <v>13177372</v>
       </c>
       <c r="G21">
-        <v>127</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -982,10 +982,10 @@
         <v>26</v>
       </c>
       <c r="E22">
-        <v>135187662</v>
+        <v>99565921</v>
       </c>
       <c r="G22">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1002,10 +1002,10 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>54397522</v>
+        <v>67046633</v>
       </c>
       <c r="G23">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1022,10 +1022,10 @@
         <v>28</v>
       </c>
       <c r="E24">
-        <v>136049338</v>
+        <v>22929445</v>
       </c>
       <c r="G24">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1042,10 +1042,10 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>131644367</v>
+        <v>82778923</v>
       </c>
       <c r="G25">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1062,10 +1062,10 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>27251306</v>
+        <v>40161087</v>
       </c>
       <c r="G26">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1082,10 +1082,10 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>92899818</v>
+        <v>122504992</v>
       </c>
       <c r="G27">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1102,10 +1102,10 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>17398913</v>
+        <v>8267132</v>
       </c>
       <c r="G28">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1122,10 +1122,10 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>70410215</v>
+        <v>78366509</v>
       </c>
       <c r="G29">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1142,10 +1142,10 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>80974007</v>
+        <v>17556086</v>
       </c>
       <c r="G30">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1162,10 +1162,10 @@
         <v>35</v>
       </c>
       <c r="E31">
-        <v>151969825</v>
+        <v>47598904</v>
       </c>
       <c r="G31">
-        <v>87</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1182,10 +1182,10 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>102945191</v>
+        <v>47962898</v>
       </c>
       <c r="G32">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1202,10 +1202,10 @@
         <v>37</v>
       </c>
       <c r="E33">
-        <v>96358026</v>
+        <v>55915815</v>
       </c>
       <c r="G33">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1222,10 +1222,10 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>27617938</v>
+        <v>75254934</v>
       </c>
       <c r="G34">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1242,10 +1242,10 @@
         <v>39</v>
       </c>
       <c r="E35">
-        <v>72851106</v>
+        <v>82132467</v>
       </c>
       <c r="G35">
-        <v>94</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1262,10 +1262,10 @@
         <v>40</v>
       </c>
       <c r="E36">
-        <v>147499353</v>
+        <v>97340641</v>
       </c>
       <c r="G36">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1282,10 +1282,10 @@
         <v>41</v>
       </c>
       <c r="E37">
-        <v>153537139</v>
+        <v>20009722</v>
       </c>
       <c r="G37">
-        <v>116</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1302,10 +1302,10 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>16393511</v>
+        <v>110888504</v>
       </c>
       <c r="G38">
-        <v>57</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1322,10 +1322,10 @@
         <v>43</v>
       </c>
       <c r="E39">
-        <v>156856006</v>
+        <v>73282933</v>
       </c>
       <c r="G39">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1342,10 +1342,10 @@
         <v>44</v>
       </c>
       <c r="E40">
-        <v>60846206</v>
+        <v>35239841</v>
       </c>
       <c r="G40">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1362,10 +1362,10 @@
         <v>45</v>
       </c>
       <c r="E41">
-        <v>32933185</v>
+        <v>87345167</v>
       </c>
       <c r="G41">
-        <v>43</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="E42">
-        <v>60349804</v>
+        <v>6141830</v>
       </c>
       <c r="G42">
-        <v>89</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1402,10 +1402,10 @@
         <v>47</v>
       </c>
       <c r="E43">
-        <v>78206839</v>
+        <v>141771670</v>
       </c>
       <c r="G43">
-        <v>80</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1422,10 +1422,10 @@
         <v>48</v>
       </c>
       <c r="E44">
-        <v>77609090</v>
+        <v>9593083</v>
       </c>
       <c r="G44">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1442,10 +1442,10 @@
         <v>49</v>
       </c>
       <c r="E45">
-        <v>90284018</v>
+        <v>164821563</v>
       </c>
       <c r="G45">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1462,10 +1462,10 @@
         <v>50</v>
       </c>
       <c r="E46">
-        <v>127241243</v>
+        <v>49067001</v>
       </c>
       <c r="G46">
-        <v>103</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1482,10 +1482,10 @@
         <v>51</v>
       </c>
       <c r="E47">
-        <v>37248399</v>
+        <v>11237443</v>
       </c>
       <c r="G47">
-        <v>73</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1502,10 +1502,10 @@
         <v>52</v>
       </c>
       <c r="E48">
-        <v>145994144</v>
+        <v>22569581</v>
       </c>
       <c r="G48">
-        <v>104</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1522,10 +1522,10 @@
         <v>53</v>
       </c>
       <c r="E49">
-        <v>72814402</v>
+        <v>76800436</v>
       </c>
       <c r="G49">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1542,10 +1542,10 @@
         <v>54</v>
       </c>
       <c r="E50">
-        <v>10625330</v>
+        <v>19095080</v>
       </c>
       <c r="G50">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1562,10 +1562,10 @@
         <v>55</v>
       </c>
       <c r="E51">
-        <v>76817265</v>
+        <v>101588024</v>
       </c>
       <c r="G51">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/src/DashboardApp/pop_final.xlsx
+++ b/src/DashboardApp/pop_final.xlsx
@@ -34,154 +34,154 @@
     <t>Diversidade</t>
   </si>
   <si>
-    <t>[1, 1, 2, 4, 16]</t>
-  </si>
-  <si>
-    <t>[14, 23, 29, 25, 29]</t>
-  </si>
-  <si>
-    <t>[30, 4, 10, 6, 26]</t>
-  </si>
-  <si>
-    <t>[5, 3, 1, 6, 29]</t>
-  </si>
-  <si>
-    <t>[15, 7, 21, 31, 19]</t>
-  </si>
-  <si>
-    <t>[13, 7, 8, 17, 7]</t>
-  </si>
-  <si>
-    <t>[22, 10, 0, 22, 25]</t>
-  </si>
-  <si>
-    <t>[4, 24, 10, 11, 16]</t>
-  </si>
-  <si>
-    <t>[24, 18, 25, 4, 23]</t>
-  </si>
-  <si>
-    <t>[8, 21, 0, 25, 1]</t>
-  </si>
-  <si>
-    <t>[24, 17, 11, 0, 23]</t>
-  </si>
-  <si>
-    <t>[22, 24, 14, 27, 23]</t>
-  </si>
-  <si>
-    <t>[14, 2, 29, 25, 1]</t>
-  </si>
-  <si>
-    <t>[12, 10, 14, 7, 9]</t>
-  </si>
-  <si>
-    <t>[1, 2, 16, 21, 23]</t>
-  </si>
-  <si>
-    <t>[19, 2, 18, 29, 27]</t>
-  </si>
-  <si>
-    <t>[2, 2, 7, 12, 17]</t>
-  </si>
-  <si>
-    <t>[13, 24, 5, 3, 4]</t>
-  </si>
-  <si>
-    <t>[14, 1, 28, 0, 9]</t>
-  </si>
-  <si>
-    <t>[10, 10, 18, 12, 4]</t>
-  </si>
-  <si>
-    <t>[17, 1, 19, 30, 4]</t>
-  </si>
-  <si>
-    <t>[3, 14, 25, 23, 1]</t>
-  </si>
-  <si>
-    <t>[12, 13, 19, 17, 22]</t>
-  </si>
-  <si>
-    <t>[24, 13, 26, 16, 22]</t>
-  </si>
-  <si>
-    <t>[12, 25, 10, 4, 15]</t>
-  </si>
-  <si>
-    <t>[28, 28, 16, 4, 3]</t>
-  </si>
-  <si>
-    <t>[7, 17, 7, 3, 11]</t>
-  </si>
-  <si>
-    <t>[1, 18, 29, 7, 21]</t>
-  </si>
-  <si>
-    <t>[18, 17, 5, 6, 19]</t>
-  </si>
-  <si>
-    <t>[4, 26, 14, 2, 3]</t>
-  </si>
-  <si>
-    <t>[21, 0, 22, 17, 31]</t>
-  </si>
-  <si>
-    <t>[20, 23, 4, 20, 24]</t>
-  </si>
-  <si>
-    <t>[3, 2, 28, 21, 29]</t>
-  </si>
-  <si>
-    <t>[13, 30, 10, 2, 21]</t>
-  </si>
-  <si>
-    <t>[11, 27, 25, 18, 7]</t>
-  </si>
-  <si>
-    <t>[9, 2, 20, 15, 12]</t>
-  </si>
-  <si>
-    <t>[23, 7, 21, 29, 25]</t>
-  </si>
-  <si>
-    <t>[15, 23, 24, 19, 5]</t>
-  </si>
-  <si>
-    <t>[11, 0, 23, 17, 15]</t>
-  </si>
-  <si>
-    <t>[26, 26, 5, 2, 17]</t>
-  </si>
-  <si>
-    <t>[14, 13, 2, 5, 19]</t>
-  </si>
-  <si>
-    <t>[28, 27, 19, 22, 9]</t>
-  </si>
-  <si>
-    <t>[13, 14, 14, 0, 19]</t>
-  </si>
-  <si>
-    <t>[6, 26, 29, 28, 30]</t>
-  </si>
-  <si>
-    <t>[17, 1, 20, 23, 14]</t>
-  </si>
-  <si>
-    <t>[4, 18, 9, 10, 10]</t>
-  </si>
-  <si>
-    <t>[5, 13, 21, 12, 4]</t>
-  </si>
-  <si>
-    <t>[12, 28, 6, 20, 14]</t>
-  </si>
-  <si>
-    <t>[6, 20, 6, 14, 9]</t>
-  </si>
-  <si>
-    <t>[17, 11, 23, 29, 17]</t>
+    <t>[0, 0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>[31, 28, 0, 8, 22]</t>
+  </si>
+  <si>
+    <t>[10, 12, 27, 3, 17]</t>
+  </si>
+  <si>
+    <t>[24, 16, 5, 26, 23]</t>
+  </si>
+  <si>
+    <t>[19, 27, 6, 27, 17]</t>
+  </si>
+  <si>
+    <t>[15, 15, 14, 4, 20]</t>
+  </si>
+  <si>
+    <t>[19, 23, 3, 27, 29]</t>
+  </si>
+  <si>
+    <t>[2, 7, 3, 13, 29]</t>
+  </si>
+  <si>
+    <t>[12, 4, 12, 13, 7]</t>
+  </si>
+  <si>
+    <t>[3, 23, 8, 7, 8]</t>
+  </si>
+  <si>
+    <t>[19, 17, 6, 6, 17]</t>
+  </si>
+  <si>
+    <t>[6, 20, 20, 6, 21]</t>
+  </si>
+  <si>
+    <t>[30, 6, 2, 10, 9]</t>
+  </si>
+  <si>
+    <t>[10, 0, 20, 1, 15]</t>
+  </si>
+  <si>
+    <t>[13, 10, 22, 11, 13]</t>
+  </si>
+  <si>
+    <t>[2, 1, 1, 7, 29]</t>
+  </si>
+  <si>
+    <t>[8, 29, 29, 0, 17]</t>
+  </si>
+  <si>
+    <t>[19, 23, 10, 21, 0]</t>
+  </si>
+  <si>
+    <t>[6, 23, 24, 9, 4]</t>
+  </si>
+  <si>
+    <t>[17, 12, 26, 21, 9]</t>
+  </si>
+  <si>
+    <t>[17, 25, 10, 6, 29]</t>
+  </si>
+  <si>
+    <t>[0, 13, 23, 27, 20]</t>
+  </si>
+  <si>
+    <t>[16, 12, 11, 5, 13]</t>
+  </si>
+  <si>
+    <t>[8, 8, 2, 8, 7]</t>
+  </si>
+  <si>
+    <t>[11, 14, 21, 24, 26]</t>
+  </si>
+  <si>
+    <t>[15, 28, 22, 5, 25]</t>
+  </si>
+  <si>
+    <t>[22, 8, 25, 24, 21]</t>
+  </si>
+  <si>
+    <t>[28, 30, 7, 5, 31]</t>
+  </si>
+  <si>
+    <t>[15, 12, 4, 11, 6]</t>
+  </si>
+  <si>
+    <t>[10, 31, 1, 24, 18]</t>
+  </si>
+  <si>
+    <t>[14, 31, 22, 16, 8]</t>
+  </si>
+  <si>
+    <t>[11, 14, 27, 4, 5]</t>
+  </si>
+  <si>
+    <t>[21, 27, 13, 25, 31]</t>
+  </si>
+  <si>
+    <t>[17, 30, 13, 7, 30]</t>
+  </si>
+  <si>
+    <t>[19, 10, 27, 11, 30]</t>
+  </si>
+  <si>
+    <t>[5, 29, 1, 28, 8]</t>
+  </si>
+  <si>
+    <t>[29, 15, 29, 10, 15]</t>
+  </si>
+  <si>
+    <t>[24, 14, 31, 19, 3]</t>
+  </si>
+  <si>
+    <t>[1, 30, 6, 12, 6]</t>
+  </si>
+  <si>
+    <t>[16, 18, 14, 28, 2]</t>
+  </si>
+  <si>
+    <t>[23, 20, 16, 18, 30]</t>
+  </si>
+  <si>
+    <t>[23, 9, 24, 20, 6]</t>
+  </si>
+  <si>
+    <t>[23, 18, 21, 18, 8]</t>
+  </si>
+  <si>
+    <t>[7, 27, 25, 13, 7]</t>
+  </si>
+  <si>
+    <t>[11, 22, 14, 22, 25]</t>
+  </si>
+  <si>
+    <t>[13, 29, 17, 3, 11]</t>
+  </si>
+  <si>
+    <t>[15, 19, 7, 28, 29]</t>
+  </si>
+  <si>
+    <t>[23, 4, 14, 13, 7]</t>
+  </si>
+  <si>
+    <t>[25, 16, 3, 7, 13]</t>
+  </si>
+  <si>
+    <t>[3, 28, 8, 9, 26]</t>
   </si>
   <si>
     <t>HOF</t>
@@ -579,13 +579,13 @@
         <v>6</v>
       </c>
       <c r="E2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
       </c>
       <c r="G2">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -602,10 +602,10 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>130102113</v>
+        <v>2293</v>
       </c>
       <c r="G3">
-        <v>120</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -622,10 +622,10 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>81179756</v>
+        <v>1271</v>
       </c>
       <c r="G4">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -642,10 +642,10 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>62245</v>
+        <v>2062</v>
       </c>
       <c r="G5">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -662,10 +662,10 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>110378732</v>
+        <v>2144</v>
       </c>
       <c r="G6">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -682,10 +682,10 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>10966285</v>
+        <v>1062</v>
       </c>
       <c r="G7">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -702,10 +702,10 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>44585064</v>
+        <v>2469</v>
       </c>
       <c r="G8">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -722,10 +722,10 @@
         <v>13</v>
       </c>
       <c r="E9">
-        <v>33937319</v>
+        <v>1072</v>
       </c>
       <c r="G9">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -742,10 +742,10 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>78646903</v>
+        <v>522</v>
       </c>
       <c r="G10">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -762,10 +762,10 @@
         <v>15</v>
       </c>
       <c r="E11">
-        <v>58634126</v>
+        <v>715</v>
       </c>
       <c r="G11">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -782,10 +782,10 @@
         <v>16</v>
       </c>
       <c r="E12">
-        <v>40494386</v>
+        <v>1011</v>
       </c>
       <c r="G12">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -802,10 +802,10 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>105445915</v>
+        <v>1313</v>
       </c>
       <c r="G13">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -822,10 +822,10 @@
         <v>18</v>
       </c>
       <c r="E14">
-        <v>109350830</v>
+        <v>1121</v>
       </c>
       <c r="G14">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -842,10 +842,10 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>6267707</v>
+        <v>726</v>
       </c>
       <c r="G15">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -862,10 +862,10 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>23010026</v>
+        <v>1043</v>
       </c>
       <c r="G16">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -882,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>87871198</v>
+        <v>896</v>
       </c>
       <c r="G17">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -902,10 +902,10 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>1751259</v>
+        <v>2035</v>
       </c>
       <c r="G18">
-        <v>40</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -922,10 +922,10 @@
         <v>23</v>
       </c>
       <c r="E19">
-        <v>34758193</v>
+        <v>1431</v>
       </c>
       <c r="G19">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -942,10 +942,10 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>65349999</v>
+        <v>1238</v>
       </c>
       <c r="G20">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -962,10 +962,10 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>13177372</v>
+        <v>1631</v>
       </c>
       <c r="G21">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -982,10 +982,10 @@
         <v>26</v>
       </c>
       <c r="E22">
-        <v>99565921</v>
+        <v>1891</v>
       </c>
       <c r="G22">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1002,10 +1002,10 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>67046633</v>
+        <v>1827</v>
       </c>
       <c r="G23">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1022,10 +1022,10 @@
         <v>28</v>
       </c>
       <c r="E24">
-        <v>22929445</v>
+        <v>715</v>
       </c>
       <c r="G24">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1042,10 +1042,10 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>82778923</v>
+        <v>245</v>
       </c>
       <c r="G25">
-        <v>101</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1062,10 +1062,10 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>40161087</v>
+        <v>2010</v>
       </c>
       <c r="G26">
-        <v>66</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1082,10 +1082,10 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>122504992</v>
+        <v>2143</v>
       </c>
       <c r="G27">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1102,10 +1102,10 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>8267132</v>
+        <v>2190</v>
       </c>
       <c r="G28">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1122,10 +1122,10 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>78366509</v>
+        <v>2719</v>
       </c>
       <c r="G29">
-        <v>76</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1142,10 +1142,10 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>17556086</v>
+        <v>542</v>
       </c>
       <c r="G30">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1162,10 +1162,10 @@
         <v>35</v>
       </c>
       <c r="E31">
-        <v>47598904</v>
+        <v>1962</v>
       </c>
       <c r="G31">
-        <v>49</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1182,7 +1182,7 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>47962898</v>
+        <v>1961</v>
       </c>
       <c r="G32">
         <v>91</v>
@@ -1202,10 +1202,10 @@
         <v>37</v>
       </c>
       <c r="E33">
-        <v>55915815</v>
+        <v>1087</v>
       </c>
       <c r="G33">
-        <v>91</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1222,10 +1222,10 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>75254934</v>
+        <v>2925</v>
       </c>
       <c r="G34">
-        <v>83</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1242,10 +1242,10 @@
         <v>39</v>
       </c>
       <c r="E35">
-        <v>82132467</v>
+        <v>2307</v>
       </c>
       <c r="G35">
-        <v>76</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1262,10 +1262,10 @@
         <v>40</v>
       </c>
       <c r="E36">
-        <v>97340641</v>
+        <v>2211</v>
       </c>
       <c r="G36">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1282,10 +1282,10 @@
         <v>41</v>
       </c>
       <c r="E37">
-        <v>20009722</v>
+        <v>1715</v>
       </c>
       <c r="G37">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1302,10 +1302,10 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>110888504</v>
+        <v>2232</v>
       </c>
       <c r="G38">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1322,10 +1322,10 @@
         <v>43</v>
       </c>
       <c r="E39">
-        <v>73282933</v>
+        <v>2103</v>
       </c>
       <c r="G39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1342,10 +1342,10 @@
         <v>44</v>
       </c>
       <c r="E40">
-        <v>35239841</v>
+        <v>1117</v>
       </c>
       <c r="G40">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1362,10 +1362,10 @@
         <v>45</v>
       </c>
       <c r="E41">
-        <v>87345167</v>
+        <v>1564</v>
       </c>
       <c r="G41">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="E42">
-        <v>6141830</v>
+        <v>2409</v>
       </c>
       <c r="G42">
-        <v>53</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1402,10 +1402,10 @@
         <v>47</v>
       </c>
       <c r="E43">
-        <v>141771670</v>
+        <v>1622</v>
       </c>
       <c r="G43">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1422,10 +1422,10 @@
         <v>48</v>
       </c>
       <c r="E44">
-        <v>9593083</v>
+        <v>1682</v>
       </c>
       <c r="G44">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1442,10 +1442,10 @@
         <v>49</v>
       </c>
       <c r="E45">
-        <v>164821563</v>
+        <v>1621</v>
       </c>
       <c r="G45">
-        <v>119</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1462,10 +1462,10 @@
         <v>50</v>
       </c>
       <c r="E46">
-        <v>49067001</v>
+        <v>1910</v>
       </c>
       <c r="G46">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1482,10 +1482,10 @@
         <v>51</v>
       </c>
       <c r="E47">
-        <v>11237443</v>
+        <v>1429</v>
       </c>
       <c r="G47">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1502,10 +1502,10 @@
         <v>52</v>
       </c>
       <c r="E48">
-        <v>22569581</v>
+        <v>2260</v>
       </c>
       <c r="G48">
-        <v>55</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1522,10 +1522,10 @@
         <v>53</v>
       </c>
       <c r="E49">
-        <v>76800436</v>
+        <v>959</v>
       </c>
       <c r="G49">
-        <v>80</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1542,10 +1542,10 @@
         <v>54</v>
       </c>
       <c r="E50">
-        <v>19095080</v>
+        <v>1108</v>
       </c>
       <c r="G50">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1562,10 +1562,10 @@
         <v>55</v>
       </c>
       <c r="E51">
-        <v>101588024</v>
+        <v>1614</v>
       </c>
       <c r="G51">
-        <v>97</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/src/DashboardApp/pop_final.xlsx
+++ b/src/DashboardApp/pop_final.xlsx
@@ -37,151 +37,151 @@
     <t>[0, 0, 0, 0, 0]</t>
   </si>
   <si>
-    <t>[31, 28, 0, 8, 22]</t>
-  </si>
-  <si>
-    <t>[10, 12, 27, 3, 17]</t>
-  </si>
-  <si>
-    <t>[24, 16, 5, 26, 23]</t>
-  </si>
-  <si>
-    <t>[19, 27, 6, 27, 17]</t>
-  </si>
-  <si>
-    <t>[15, 15, 14, 4, 20]</t>
-  </si>
-  <si>
-    <t>[19, 23, 3, 27, 29]</t>
-  </si>
-  <si>
-    <t>[2, 7, 3, 13, 29]</t>
-  </si>
-  <si>
-    <t>[12, 4, 12, 13, 7]</t>
-  </si>
-  <si>
-    <t>[3, 23, 8, 7, 8]</t>
-  </si>
-  <si>
-    <t>[19, 17, 6, 6, 17]</t>
-  </si>
-  <si>
-    <t>[6, 20, 20, 6, 21]</t>
-  </si>
-  <si>
-    <t>[30, 6, 2, 10, 9]</t>
-  </si>
-  <si>
-    <t>[10, 0, 20, 1, 15]</t>
-  </si>
-  <si>
-    <t>[13, 10, 22, 11, 13]</t>
-  </si>
-  <si>
-    <t>[2, 1, 1, 7, 29]</t>
-  </si>
-  <si>
-    <t>[8, 29, 29, 0, 17]</t>
-  </si>
-  <si>
-    <t>[19, 23, 10, 21, 0]</t>
-  </si>
-  <si>
-    <t>[6, 23, 24, 9, 4]</t>
-  </si>
-  <si>
-    <t>[17, 12, 26, 21, 9]</t>
-  </si>
-  <si>
-    <t>[17, 25, 10, 6, 29]</t>
-  </si>
-  <si>
-    <t>[0, 13, 23, 27, 20]</t>
-  </si>
-  <si>
-    <t>[16, 12, 11, 5, 13]</t>
-  </si>
-  <si>
-    <t>[8, 8, 2, 8, 7]</t>
-  </si>
-  <si>
-    <t>[11, 14, 21, 24, 26]</t>
-  </si>
-  <si>
-    <t>[15, 28, 22, 5, 25]</t>
-  </si>
-  <si>
-    <t>[22, 8, 25, 24, 21]</t>
-  </si>
-  <si>
-    <t>[28, 30, 7, 5, 31]</t>
-  </si>
-  <si>
-    <t>[15, 12, 4, 11, 6]</t>
-  </si>
-  <si>
-    <t>[10, 31, 1, 24, 18]</t>
-  </si>
-  <si>
-    <t>[14, 31, 22, 16, 8]</t>
-  </si>
-  <si>
-    <t>[11, 14, 27, 4, 5]</t>
-  </si>
-  <si>
-    <t>[21, 27, 13, 25, 31]</t>
-  </si>
-  <si>
-    <t>[17, 30, 13, 7, 30]</t>
-  </si>
-  <si>
-    <t>[19, 10, 27, 11, 30]</t>
-  </si>
-  <si>
-    <t>[5, 29, 1, 28, 8]</t>
-  </si>
-  <si>
-    <t>[29, 15, 29, 10, 15]</t>
-  </si>
-  <si>
-    <t>[24, 14, 31, 19, 3]</t>
-  </si>
-  <si>
-    <t>[1, 30, 6, 12, 6]</t>
-  </si>
-  <si>
-    <t>[16, 18, 14, 28, 2]</t>
-  </si>
-  <si>
-    <t>[23, 20, 16, 18, 30]</t>
-  </si>
-  <si>
-    <t>[23, 9, 24, 20, 6]</t>
-  </si>
-  <si>
-    <t>[23, 18, 21, 18, 8]</t>
-  </si>
-  <si>
-    <t>[7, 27, 25, 13, 7]</t>
-  </si>
-  <si>
-    <t>[11, 22, 14, 22, 25]</t>
-  </si>
-  <si>
-    <t>[13, 29, 17, 3, 11]</t>
-  </si>
-  <si>
-    <t>[15, 19, 7, 28, 29]</t>
-  </si>
-  <si>
-    <t>[23, 4, 14, 13, 7]</t>
-  </si>
-  <si>
-    <t>[25, 16, 3, 7, 13]</t>
-  </si>
-  <si>
-    <t>[3, 28, 8, 9, 26]</t>
+    <t>[7, 26, 8, 13, 3]</t>
+  </si>
+  <si>
+    <t>[5, 0, 30, 26, 14]</t>
+  </si>
+  <si>
+    <t>[28, 5, 1, 5, 17]</t>
+  </si>
+  <si>
+    <t>[9, 30, 19, 8, 21]</t>
+  </si>
+  <si>
+    <t>[2, 4, 12, 0, 16]</t>
+  </si>
+  <si>
+    <t>[1, 2, 24, 21, 10]</t>
+  </si>
+  <si>
+    <t>[0, 5, 13, 19, 1]</t>
+  </si>
+  <si>
+    <t>[15, 6, 22, 31, 23]</t>
+  </si>
+  <si>
+    <t>[20, 7, 14, 17, 31]</t>
+  </si>
+  <si>
+    <t>[23, 21, 7, 25, 5]</t>
+  </si>
+  <si>
+    <t>[7, 3, 23, 30, 17]</t>
+  </si>
+  <si>
+    <t>[11, 31, 14, 6, 22]</t>
+  </si>
+  <si>
+    <t>[27, 7, 17, 23, 24]</t>
+  </si>
+  <si>
+    <t>[26, 4, 5, 31, 18]</t>
+  </si>
+  <si>
+    <t>[12, 12, 22, 10, 4]</t>
+  </si>
+  <si>
+    <t>[5, 26, 25, 16, 5]</t>
+  </si>
+  <si>
+    <t>[16, 25, 20, 19, 10]</t>
+  </si>
+  <si>
+    <t>[4, 6, 27, 27, 21]</t>
+  </si>
+  <si>
+    <t>[13, 7, 21, 2, 6]</t>
+  </si>
+  <si>
+    <t>[31, 10, 0, 0, 13]</t>
+  </si>
+  <si>
+    <t>[17, 19, 26, 25, 8]</t>
+  </si>
+  <si>
+    <t>[8, 24, 15, 7, 8]</t>
+  </si>
+  <si>
+    <t>[14, 19, 21, 11, 15]</t>
+  </si>
+  <si>
+    <t>[5, 18, 18, 4, 23]</t>
+  </si>
+  <si>
+    <t>[5, 31, 23, 0, 8]</t>
+  </si>
+  <si>
+    <t>[20, 26, 25, 25, 13]</t>
+  </si>
+  <si>
+    <t>[25, 18, 26, 5, 31]</t>
+  </si>
+  <si>
+    <t>[11, 22, 11, 17, 16]</t>
+  </si>
+  <si>
+    <t>[4, 16, 4, 20, 17]</t>
+  </si>
+  <si>
+    <t>[20, 25, 17, 21, 4]</t>
+  </si>
+  <si>
+    <t>[9, 26, 15, 26, 28]</t>
+  </si>
+  <si>
+    <t>[17, 10, 28, 22, 24]</t>
+  </si>
+  <si>
+    <t>[12, 7, 23, 13, 18]</t>
+  </si>
+  <si>
+    <t>[25, 23, 26, 16, 16]</t>
+  </si>
+  <si>
+    <t>[5, 0, 28, 0, 20]</t>
+  </si>
+  <si>
+    <t>[21, 11, 9, 31, 24]</t>
+  </si>
+  <si>
+    <t>[15, 29, 26, 17, 22]</t>
+  </si>
+  <si>
+    <t>[29, 31, 20, 13, 6]</t>
+  </si>
+  <si>
+    <t>[23, 13, 15, 1, 26]</t>
+  </si>
+  <si>
+    <t>[30, 9, 29, 14, 11]</t>
+  </si>
+  <si>
+    <t>[20, 19, 28, 9, 0]</t>
+  </si>
+  <si>
+    <t>[3, 18, 29, 27, 16]</t>
+  </si>
+  <si>
+    <t>[27, 9, 24, 16, 1]</t>
+  </si>
+  <si>
+    <t>[17, 18, 25, 29, 11]</t>
+  </si>
+  <si>
+    <t>[12, 23, 9, 15, 22]</t>
+  </si>
+  <si>
+    <t>[21, 23, 7, 20, 3]</t>
+  </si>
+  <si>
+    <t>[16, 24, 6, 30, 8]</t>
+  </si>
+  <si>
+    <t>[20, 27, 19, 23, 17]</t>
+  </si>
+  <si>
+    <t>[31, 13, 14, 8, 14]</t>
   </si>
   <si>
     <t>HOF</t>
@@ -602,10 +602,10 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>2293</v>
+        <v>967</v>
       </c>
       <c r="G3">
-        <v>89</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -622,10 +622,10 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>1271</v>
+        <v>1797</v>
       </c>
       <c r="G4">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -642,10 +642,10 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>2062</v>
+        <v>1124</v>
       </c>
       <c r="G5">
-        <v>94</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -662,10 +662,10 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>2144</v>
+        <v>1847</v>
       </c>
       <c r="G6">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -682,10 +682,10 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>1062</v>
+        <v>420</v>
       </c>
       <c r="G7">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -702,10 +702,10 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>2469</v>
+        <v>1122</v>
       </c>
       <c r="G8">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -722,10 +722,10 @@
         <v>13</v>
       </c>
       <c r="E9">
-        <v>1072</v>
+        <v>556</v>
       </c>
       <c r="G9">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -742,10 +742,10 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>522</v>
+        <v>2235</v>
       </c>
       <c r="G10">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -762,10 +762,10 @@
         <v>15</v>
       </c>
       <c r="E11">
-        <v>715</v>
+        <v>1895</v>
       </c>
       <c r="G11">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -782,10 +782,10 @@
         <v>16</v>
       </c>
       <c r="E12">
-        <v>1011</v>
+        <v>1669</v>
       </c>
       <c r="G12">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -802,10 +802,10 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>1313</v>
+        <v>1776</v>
       </c>
       <c r="G13">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -822,10 +822,10 @@
         <v>18</v>
       </c>
       <c r="E14">
-        <v>1121</v>
+        <v>1798</v>
       </c>
       <c r="G14">
-        <v>57</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -842,10 +842,10 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>726</v>
+        <v>2172</v>
       </c>
       <c r="G15">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -862,10 +862,10 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>1043</v>
+        <v>2002</v>
       </c>
       <c r="G16">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -882,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="G17">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -902,10 +902,10 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>2035</v>
+        <v>1607</v>
       </c>
       <c r="G18">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -922,10 +922,10 @@
         <v>23</v>
       </c>
       <c r="E19">
-        <v>1431</v>
+        <v>1742</v>
       </c>
       <c r="G19">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -942,10 +942,10 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>1238</v>
+        <v>1951</v>
       </c>
       <c r="G20">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -962,10 +962,10 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>1631</v>
+        <v>699</v>
       </c>
       <c r="G21">
-        <v>85</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -982,10 +982,10 @@
         <v>26</v>
       </c>
       <c r="E22">
-        <v>1891</v>
+        <v>1230</v>
       </c>
       <c r="G22">
-        <v>87</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1002,10 +1002,10 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>1827</v>
+        <v>2015</v>
       </c>
       <c r="G23">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1022,10 +1022,10 @@
         <v>28</v>
       </c>
       <c r="E24">
-        <v>715</v>
+        <v>978</v>
       </c>
       <c r="G24">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1042,10 +1042,10 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>245</v>
+        <v>1344</v>
       </c>
       <c r="G25">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1062,10 +1062,10 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>2010</v>
+        <v>1218</v>
       </c>
       <c r="G26">
-        <v>96</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1082,10 +1082,10 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>2143</v>
+        <v>1579</v>
       </c>
       <c r="G27">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1102,10 +1102,10 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>2190</v>
+        <v>2495</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1122,10 +1122,10 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>2719</v>
+        <v>2611</v>
       </c>
       <c r="G29">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1142,10 +1142,10 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>542</v>
+        <v>1271</v>
       </c>
       <c r="G30">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1162,10 +1162,10 @@
         <v>35</v>
       </c>
       <c r="E31">
-        <v>1962</v>
+        <v>977</v>
       </c>
       <c r="G31">
-        <v>84</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1182,10 +1182,10 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>1961</v>
+        <v>1771</v>
       </c>
       <c r="G32">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1202,10 +1202,10 @@
         <v>37</v>
       </c>
       <c r="E33">
-        <v>1087</v>
+        <v>2442</v>
       </c>
       <c r="G33">
-        <v>61</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1222,10 +1222,10 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>2925</v>
+        <v>2233</v>
       </c>
       <c r="G34">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1242,10 +1242,10 @@
         <v>39</v>
       </c>
       <c r="E35">
-        <v>2307</v>
+        <v>1215</v>
       </c>
       <c r="G35">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1262,10 +1262,10 @@
         <v>40</v>
       </c>
       <c r="E36">
-        <v>2211</v>
+        <v>2342</v>
       </c>
       <c r="G36">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1282,10 +1282,10 @@
         <v>41</v>
       </c>
       <c r="E37">
-        <v>1715</v>
+        <v>1209</v>
       </c>
       <c r="G37">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1302,10 +1302,10 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>2232</v>
+        <v>2180</v>
       </c>
       <c r="G38">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1322,10 +1322,10 @@
         <v>43</v>
       </c>
       <c r="E39">
-        <v>2103</v>
+        <v>2515</v>
       </c>
       <c r="G39">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1342,10 +1342,10 @@
         <v>44</v>
       </c>
       <c r="E40">
-        <v>1117</v>
+        <v>2407</v>
       </c>
       <c r="G40">
-        <v>55</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1362,7 +1362,7 @@
         <v>45</v>
       </c>
       <c r="E41">
-        <v>1564</v>
+        <v>1600</v>
       </c>
       <c r="G41">
         <v>78</v>
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="E42">
-        <v>2409</v>
+        <v>2139</v>
       </c>
       <c r="G42">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1402,10 +1402,10 @@
         <v>47</v>
       </c>
       <c r="E43">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="G43">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1422,10 +1422,10 @@
         <v>48</v>
       </c>
       <c r="E44">
-        <v>1682</v>
+        <v>2159</v>
       </c>
       <c r="G44">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1442,10 +1442,10 @@
         <v>49</v>
       </c>
       <c r="E45">
-        <v>1621</v>
+        <v>1643</v>
       </c>
       <c r="G45">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1462,10 +1462,10 @@
         <v>50</v>
       </c>
       <c r="E46">
-        <v>1910</v>
+        <v>2200</v>
       </c>
       <c r="G46">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1482,10 +1482,10 @@
         <v>51</v>
       </c>
       <c r="E47">
-        <v>1429</v>
+        <v>1463</v>
       </c>
       <c r="G47">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1502,10 +1502,10 @@
         <v>52</v>
       </c>
       <c r="E48">
-        <v>2260</v>
+        <v>1428</v>
       </c>
       <c r="G48">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1522,10 +1522,10 @@
         <v>53</v>
       </c>
       <c r="E49">
-        <v>959</v>
+        <v>1832</v>
       </c>
       <c r="G49">
-        <v>61</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1542,10 +1542,10 @@
         <v>54</v>
       </c>
       <c r="E50">
-        <v>1108</v>
+        <v>2308</v>
       </c>
       <c r="G50">
-        <v>64</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1562,10 +1562,10 @@
         <v>55</v>
       </c>
       <c r="E51">
-        <v>1614</v>
+        <v>1586</v>
       </c>
       <c r="G51">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/src/DashboardApp/pop_final.xlsx
+++ b/src/DashboardApp/pop_final.xlsx
@@ -37,151 +37,151 @@
     <t>[0, 0, 0, 0, 0]</t>
   </si>
   <si>
-    <t>[7, 26, 8, 13, 3]</t>
-  </si>
-  <si>
-    <t>[5, 0, 30, 26, 14]</t>
-  </si>
-  <si>
-    <t>[28, 5, 1, 5, 17]</t>
-  </si>
-  <si>
-    <t>[9, 30, 19, 8, 21]</t>
-  </si>
-  <si>
-    <t>[2, 4, 12, 0, 16]</t>
-  </si>
-  <si>
-    <t>[1, 2, 24, 21, 10]</t>
-  </si>
-  <si>
-    <t>[0, 5, 13, 19, 1]</t>
-  </si>
-  <si>
-    <t>[15, 6, 22, 31, 23]</t>
-  </si>
-  <si>
-    <t>[20, 7, 14, 17, 31]</t>
-  </si>
-  <si>
-    <t>[23, 21, 7, 25, 5]</t>
-  </si>
-  <si>
-    <t>[7, 3, 23, 30, 17]</t>
-  </si>
-  <si>
-    <t>[11, 31, 14, 6, 22]</t>
-  </si>
-  <si>
-    <t>[27, 7, 17, 23, 24]</t>
-  </si>
-  <si>
-    <t>[26, 4, 5, 31, 18]</t>
-  </si>
-  <si>
-    <t>[12, 12, 22, 10, 4]</t>
-  </si>
-  <si>
-    <t>[5, 26, 25, 16, 5]</t>
-  </si>
-  <si>
-    <t>[16, 25, 20, 19, 10]</t>
-  </si>
-  <si>
-    <t>[4, 6, 27, 27, 21]</t>
-  </si>
-  <si>
-    <t>[13, 7, 21, 2, 6]</t>
-  </si>
-  <si>
-    <t>[31, 10, 0, 0, 13]</t>
-  </si>
-  <si>
-    <t>[17, 19, 26, 25, 8]</t>
-  </si>
-  <si>
-    <t>[8, 24, 15, 7, 8]</t>
-  </si>
-  <si>
-    <t>[14, 19, 21, 11, 15]</t>
-  </si>
-  <si>
-    <t>[5, 18, 18, 4, 23]</t>
-  </si>
-  <si>
-    <t>[5, 31, 23, 0, 8]</t>
-  </si>
-  <si>
-    <t>[20, 26, 25, 25, 13]</t>
-  </si>
-  <si>
-    <t>[25, 18, 26, 5, 31]</t>
-  </si>
-  <si>
-    <t>[11, 22, 11, 17, 16]</t>
-  </si>
-  <si>
-    <t>[4, 16, 4, 20, 17]</t>
-  </si>
-  <si>
-    <t>[20, 25, 17, 21, 4]</t>
-  </si>
-  <si>
-    <t>[9, 26, 15, 26, 28]</t>
-  </si>
-  <si>
-    <t>[17, 10, 28, 22, 24]</t>
-  </si>
-  <si>
-    <t>[12, 7, 23, 13, 18]</t>
-  </si>
-  <si>
-    <t>[25, 23, 26, 16, 16]</t>
-  </si>
-  <si>
-    <t>[5, 0, 28, 0, 20]</t>
-  </si>
-  <si>
-    <t>[21, 11, 9, 31, 24]</t>
-  </si>
-  <si>
-    <t>[15, 29, 26, 17, 22]</t>
-  </si>
-  <si>
-    <t>[29, 31, 20, 13, 6]</t>
-  </si>
-  <si>
-    <t>[23, 13, 15, 1, 26]</t>
-  </si>
-  <si>
-    <t>[30, 9, 29, 14, 11]</t>
-  </si>
-  <si>
-    <t>[20, 19, 28, 9, 0]</t>
-  </si>
-  <si>
-    <t>[3, 18, 29, 27, 16]</t>
-  </si>
-  <si>
-    <t>[27, 9, 24, 16, 1]</t>
-  </si>
-  <si>
-    <t>[17, 18, 25, 29, 11]</t>
-  </si>
-  <si>
-    <t>[12, 23, 9, 15, 22]</t>
-  </si>
-  <si>
-    <t>[21, 23, 7, 20, 3]</t>
-  </si>
-  <si>
-    <t>[16, 24, 6, 30, 8]</t>
-  </si>
-  <si>
-    <t>[20, 27, 19, 23, 17]</t>
-  </si>
-  <si>
-    <t>[31, 13, 14, 8, 14]</t>
+    <t>[23, 0, 25, 20, 6]</t>
+  </si>
+  <si>
+    <t>[19, 23, 21, 27, 30]</t>
+  </si>
+  <si>
+    <t>[17, 24, 12, 5, 27]</t>
+  </si>
+  <si>
+    <t>[3, 12, 27, 23, 29]</t>
+  </si>
+  <si>
+    <t>[25, 17, 26, 26, 30]</t>
+  </si>
+  <si>
+    <t>[12, 31, 12, 3, 23]</t>
+  </si>
+  <si>
+    <t>[1, 11, 7, 5, 8]</t>
+  </si>
+  <si>
+    <t>[31, 19, 28, 8, 9]</t>
+  </si>
+  <si>
+    <t>[21, 6, 12, 10, 3]</t>
+  </si>
+  <si>
+    <t>[4, 30, 28, 22, 7]</t>
+  </si>
+  <si>
+    <t>[28, 23, 17, 6, 13]</t>
+  </si>
+  <si>
+    <t>[21, 9, 5, 8, 31]</t>
+  </si>
+  <si>
+    <t>[27, 10, 20, 6, 28]</t>
+  </si>
+  <si>
+    <t>[27, 8, 11, 13, 9]</t>
+  </si>
+  <si>
+    <t>[27, 6, 26, 8, 18]</t>
+  </si>
+  <si>
+    <t>[30, 10, 4, 9, 30]</t>
+  </si>
+  <si>
+    <t>[7, 24, 22, 17, 8]</t>
+  </si>
+  <si>
+    <t>[13, 15, 18, 1, 20]</t>
+  </si>
+  <si>
+    <t>[26, 18, 12, 1, 12]</t>
+  </si>
+  <si>
+    <t>[5, 27, 8, 8, 11]</t>
+  </si>
+  <si>
+    <t>[24, 6, 8, 5, 0]</t>
+  </si>
+  <si>
+    <t>[20, 4, 3, 27, 9]</t>
+  </si>
+  <si>
+    <t>[14, 7, 30, 27, 4]</t>
+  </si>
+  <si>
+    <t>[21, 18, 30, 23, 23]</t>
+  </si>
+  <si>
+    <t>[11, 24, 16, 17, 9]</t>
+  </si>
+  <si>
+    <t>[31, 20, 18, 4, 10]</t>
+  </si>
+  <si>
+    <t>[9, 1, 27, 28, 3]</t>
+  </si>
+  <si>
+    <t>[17, 12, 1, 27, 28]</t>
+  </si>
+  <si>
+    <t>[17, 11, 1, 1, 20]</t>
+  </si>
+  <si>
+    <t>[6, 6, 23, 18, 14]</t>
+  </si>
+  <si>
+    <t>[20, 28, 28, 11, 10]</t>
+  </si>
+  <si>
+    <t>[20, 2, 15, 18, 12]</t>
+  </si>
+  <si>
+    <t>[30, 20, 2, 18, 8]</t>
+  </si>
+  <si>
+    <t>[20, 9, 5, 28, 14]</t>
+  </si>
+  <si>
+    <t>[23, 7, 2, 11, 24]</t>
+  </si>
+  <si>
+    <t>[7, 4, 17, 5, 23]</t>
+  </si>
+  <si>
+    <t>[30, 20, 19, 8, 27]</t>
+  </si>
+  <si>
+    <t>[23, 24, 7, 13, 1]</t>
+  </si>
+  <si>
+    <t>[3, 7, 8, 8, 20]</t>
+  </si>
+  <si>
+    <t>[8, 16, 11, 7, 31]</t>
+  </si>
+  <si>
+    <t>[12, 8, 9, 14, 8]</t>
+  </si>
+  <si>
+    <t>[13, 5, 4, 19, 6]</t>
+  </si>
+  <si>
+    <t>[14, 14, 27, 5, 7]</t>
+  </si>
+  <si>
+    <t>[13, 30, 19, 16, 23]</t>
+  </si>
+  <si>
+    <t>[15, 22, 13, 20, 20]</t>
+  </si>
+  <si>
+    <t>[12, 17, 8, 19, 25]</t>
+  </si>
+  <si>
+    <t>[19, 24, 26, 9, 22]</t>
+  </si>
+  <si>
+    <t>[26, 29, 18, 14, 29]</t>
+  </si>
+  <si>
+    <t>[23, 30, 0, 19, 28]</t>
   </si>
   <si>
     <t>HOF</t>
@@ -602,10 +602,10 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>967</v>
+        <v>1590</v>
       </c>
       <c r="G3">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -622,10 +622,10 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>1797</v>
+        <v>2960</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -642,10 +642,10 @@
         <v>9</v>
       </c>
       <c r="E5">
-        <v>1124</v>
+        <v>1763</v>
       </c>
       <c r="G5">
-        <v>56</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -662,10 +662,10 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>1847</v>
+        <v>2252</v>
       </c>
       <c r="G6">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -682,10 +682,10 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>420</v>
+        <v>3166</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -702,10 +702,10 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>1122</v>
+        <v>1787</v>
       </c>
       <c r="G8">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -722,10 +722,10 @@
         <v>13</v>
       </c>
       <c r="E9">
-        <v>556</v>
+        <v>260</v>
       </c>
       <c r="G9">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -742,10 +742,10 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>2235</v>
+        <v>2251</v>
       </c>
       <c r="G10">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -762,10 +762,10 @@
         <v>15</v>
       </c>
       <c r="E11">
-        <v>1895</v>
+        <v>730</v>
       </c>
       <c r="G11">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -782,10 +782,10 @@
         <v>16</v>
       </c>
       <c r="E12">
-        <v>1669</v>
+        <v>2233</v>
       </c>
       <c r="G12">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -802,10 +802,10 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>1776</v>
+        <v>1807</v>
       </c>
       <c r="G13">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -822,10 +822,10 @@
         <v>18</v>
       </c>
       <c r="E14">
-        <v>1798</v>
+        <v>1572</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -842,10 +842,10 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>2172</v>
+        <v>2049</v>
       </c>
       <c r="G15">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -862,10 +862,10 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>2002</v>
+        <v>1164</v>
       </c>
       <c r="G16">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -882,10 +882,10 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>888</v>
+        <v>1829</v>
       </c>
       <c r="G17">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -902,10 +902,10 @@
         <v>22</v>
       </c>
       <c r="E18">
-        <v>1607</v>
+        <v>1997</v>
       </c>
       <c r="G18">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -922,10 +922,10 @@
         <v>23</v>
       </c>
       <c r="E19">
-        <v>1742</v>
+        <v>1462</v>
       </c>
       <c r="G19">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -942,10 +942,10 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>1951</v>
+        <v>1119</v>
       </c>
       <c r="G20">
-        <v>85</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -962,10 +962,10 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>699</v>
+        <v>1289</v>
       </c>
       <c r="G21">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -982,10 +982,10 @@
         <v>26</v>
       </c>
       <c r="E22">
-        <v>1230</v>
+        <v>1003</v>
       </c>
       <c r="G22">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1002,10 +1002,10 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>2015</v>
+        <v>701</v>
       </c>
       <c r="G23">
-        <v>95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1022,10 +1022,10 @@
         <v>28</v>
       </c>
       <c r="E24">
-        <v>978</v>
+        <v>1235</v>
       </c>
       <c r="G24">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1042,10 +1042,10 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>1344</v>
+        <v>1890</v>
       </c>
       <c r="G25">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1062,10 +1062,10 @@
         <v>30</v>
       </c>
       <c r="E26">
-        <v>1218</v>
+        <v>2723</v>
       </c>
       <c r="G26">
-        <v>68</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1082,10 +1082,10 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>1579</v>
+        <v>1323</v>
       </c>
       <c r="G27">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1102,10 +1102,10 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>2495</v>
+        <v>1801</v>
       </c>
       <c r="G28">
-        <v>109</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1122,10 +1122,10 @@
         <v>33</v>
       </c>
       <c r="E29">
-        <v>2611</v>
+        <v>1604</v>
       </c>
       <c r="G29">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1142,10 +1142,10 @@
         <v>34</v>
       </c>
       <c r="E30">
-        <v>1271</v>
+        <v>1947</v>
       </c>
       <c r="G30">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1162,10 +1162,10 @@
         <v>35</v>
       </c>
       <c r="E31">
-        <v>977</v>
+        <v>812</v>
       </c>
       <c r="G31">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1182,10 +1182,10 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>1771</v>
+        <v>1121</v>
       </c>
       <c r="G32">
-        <v>87</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1202,10 +1202,10 @@
         <v>37</v>
       </c>
       <c r="E33">
-        <v>2442</v>
+        <v>2189</v>
       </c>
       <c r="G33">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1222,10 +1222,10 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>2233</v>
+        <v>1097</v>
       </c>
       <c r="G34">
-        <v>101</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1242,10 +1242,10 @@
         <v>39</v>
       </c>
       <c r="E35">
-        <v>1215</v>
+        <v>1692</v>
       </c>
       <c r="G35">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1262,10 +1262,10 @@
         <v>40</v>
       </c>
       <c r="E36">
-        <v>2342</v>
+        <v>1486</v>
       </c>
       <c r="G36">
-        <v>106</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1282,10 +1282,10 @@
         <v>41</v>
       </c>
       <c r="E37">
-        <v>1209</v>
+        <v>1279</v>
       </c>
       <c r="G37">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1302,10 +1302,10 @@
         <v>42</v>
       </c>
       <c r="E38">
-        <v>2180</v>
+        <v>908</v>
       </c>
       <c r="G38">
-        <v>96</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1322,10 +1322,10 @@
         <v>43</v>
       </c>
       <c r="E39">
-        <v>2515</v>
+        <v>2454</v>
       </c>
       <c r="G39">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1342,10 +1342,10 @@
         <v>44</v>
       </c>
       <c r="E40">
-        <v>2407</v>
+        <v>1324</v>
       </c>
       <c r="G40">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1362,10 +1362,10 @@
         <v>45</v>
       </c>
       <c r="E41">
-        <v>1600</v>
+        <v>586</v>
       </c>
       <c r="G41">
-        <v>78</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="E42">
-        <v>2139</v>
+        <v>1451</v>
       </c>
       <c r="G42">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1402,10 +1402,10 @@
         <v>47</v>
       </c>
       <c r="E43">
-        <v>1626</v>
+        <v>549</v>
       </c>
       <c r="G43">
-        <v>76</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1422,10 +1422,10 @@
         <v>48</v>
       </c>
       <c r="E44">
-        <v>2159</v>
+        <v>607</v>
       </c>
       <c r="G44">
-        <v>93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1442,10 +1442,10 @@
         <v>49</v>
       </c>
       <c r="E45">
-        <v>1643</v>
+        <v>1195</v>
       </c>
       <c r="G45">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1462,10 +1462,10 @@
         <v>50</v>
       </c>
       <c r="E46">
-        <v>2200</v>
+        <v>2215</v>
       </c>
       <c r="G46">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1482,10 +1482,10 @@
         <v>51</v>
       </c>
       <c r="E47">
-        <v>1463</v>
+        <v>1678</v>
       </c>
       <c r="G47">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1502,10 +1502,10 @@
         <v>52</v>
       </c>
       <c r="E48">
-        <v>1428</v>
+        <v>1483</v>
       </c>
       <c r="G48">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1522,10 +1522,10 @@
         <v>53</v>
       </c>
       <c r="E49">
-        <v>1832</v>
+        <v>2178</v>
       </c>
       <c r="G49">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1542,10 +1542,10 @@
         <v>54</v>
       </c>
       <c r="E50">
-        <v>2308</v>
+        <v>2878</v>
       </c>
       <c r="G50">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1562,10 +1562,10 @@
         <v>55</v>
       </c>
       <c r="E51">
-        <v>1586</v>
+        <v>2574</v>
       </c>
       <c r="G51">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/src/DashboardApp/pop_final.xlsx
+++ b/src/DashboardApp/pop_final.xlsx
@@ -472,11 +472,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[30, 26, 30, 30, 26]</t>
+          <t>[24, 30, 24, 24, 31]</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>331.9586580527748</v>
+        <v>310.8114961272593</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
@@ -499,15 +499,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[21, 16, 30, 23, 17]</t>
+          <t>[12, 23, 1, 14, 26]</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1208.605954301698</v>
+        <v>1260.17181808593</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>107</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -522,15 +522,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[1, 15, 11, 2, 4]</t>
+          <t>[14, 21, 17, 29, 31]</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1084.20342719836</v>
+        <v>1477.162186168359</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5">
@@ -545,15 +545,15 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[2, 1, 29, 11, 26]</t>
+          <t>[19, 15, 7, 0, 31]</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1055.5202493735</v>
+        <v>1169.982749926367</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -568,15 +568,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[27, 23, 6, 0, 29]</t>
+          <t>[26, 3, 4, 2, 9]</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1027.00248883782</v>
+        <v>1078.03770839458</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -591,15 +591,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[2, 7, 2, 18, 8]</t>
+          <t>[2, 21, 0, 13, 0]</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>647.8904815159173</v>
+        <v>1056.908492905307</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -614,15 +614,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[30, 12, 19, 25, 16]</t>
+          <t>[26, 22, 0, 19, 5]</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1352.621107357681</v>
+        <v>1373.221229390387</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -637,15 +637,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[21, 6, 2, 21, 14]</t>
+          <t>[16, 17, 22, 6, 9]</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>893.9732541300325</v>
+        <v>1244.552579233342</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -660,15 +660,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[12, 25, 25, 21, 15]</t>
+          <t>[13, 13, 14, 7, 10]</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1167.876040958939</v>
+        <v>1170.638749770362</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>98</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -683,15 +683,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[6, 11, 20, 12, 24]</t>
+          <t>[11, 2, 19, 8, 30]</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1270.657391937014</v>
+        <v>952.3274916823859</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
